--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -3382,19 +3382,19 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>20822000</v>
+        <v>19052000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>37116</v>
+        <v>33961</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>33 套</t>
+          <t>32 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>60 套</t>
+          <t>61 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -6437,12 +6437,12 @@
       <c r="E10" s="16" t="inlineStr"/>
       <c r="F10" s="16" t="inlineStr"/>
       <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
-$2,082万
-$37,116/呎
-(在售)</t>
+$1,905万
+$33,961/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
@@ -6580,7 +6580,7 @@
           <t>D6 | 1579呎 (4+房)
 $5,211万
 $33,000/呎
-(26年-06月)</t>
+(已售)</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -6752,7 +6752,7 @@
           <t>D2 | 1605呎 (4+房)
 $4,687万
 $29,200/呎
-(26年-06月)</t>
+(已售)</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -6932,7 +6932,7 @@
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1/F</t>
+          <t>B&amp;G&amp;1/F</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr"/>
@@ -6949,31 +6949,17 @@
       <c r="M15" s="16" t="inlineStr"/>
       <c r="N15" s="16" t="inlineStr"/>
       <c r="O15" s="16" t="inlineStr"/>
-      <c r="P15" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1,876万
-$32,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="Q15" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="R15" s="16" t="inlineStr"/>
+      <c r="S15" s="18" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4,545万
-$39,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S15" s="16" t="inlineStr"/>
       <c r="T15" s="16" t="inlineStr"/>
       <c r="U15" s="16" t="inlineStr"/>
       <c r="V15" s="16" t="inlineStr"/>
@@ -6981,7 +6967,7 @@
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1/F</t>
+          <t>1/F</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr"/>
@@ -6998,17 +6984,31 @@
       <c r="M16" s="16" t="inlineStr"/>
       <c r="N16" s="16" t="inlineStr"/>
       <c r="O16" s="16" t="inlineStr"/>
-      <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr"/>
-      <c r="R16" s="16" t="inlineStr"/>
-      <c r="S16" s="18" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P16" s="19" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1,876万
+$32,022/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R16" s="19" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4,545万
+$39,800/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="S16" s="16" t="inlineStr"/>
       <c r="T16" s="16" t="inlineStr"/>
       <c r="U16" s="16" t="inlineStr"/>
       <c r="V16" s="16" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="滶蕴 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,7 +1141,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1323,7 +1187,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1369,7 +1233,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1515,7 +1379,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1661,7 +1525,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1845,7 +1709,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1987,7 +1851,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2033,7 +1897,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2079,7 +1943,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2125,7 +1989,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2171,7 +2035,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2217,7 +2081,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2263,7 +2127,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2501,7 +2365,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2685,7 +2549,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2777,7 +2641,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2873,7 +2737,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2919,7 +2783,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3015,7 +2879,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3061,7 +2925,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3157,7 +3021,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3341,7 +3205,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3433,7 +3297,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3479,7 +3343,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3525,7 +3389,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3571,7 +3435,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3617,7 +3481,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3663,7 +3527,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3759,7 +3623,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3805,7 +3669,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3901,7 +3765,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3947,7 +3811,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4085,7 +3949,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4131,7 +3995,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4177,7 +4041,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4269,7 +4133,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4365,7 +4229,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4411,7 +4275,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4507,7 +4371,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4603,7 +4467,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4925,7 +4789,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4971,7 +4835,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5017,7 +4881,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5063,7 +4927,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5109,7 +4973,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5155,7 +5019,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5251,7 +5115,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5347,7 +5211,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5393,7 +5257,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5439,7 +5303,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5485,7 +5349,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5531,7 +5395,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5577,7 +5441,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5623,7 +5487,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5669,7 +5533,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5787,1356 +5651,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>滶蕴 - 滶蕴 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>109 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>32 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>61 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>E6</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>ROSA VILLA</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>E1 | 560呎 (2房)
-$2,206万
-$39,388/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,724万
-$39,637/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,795万
-$38,264/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1,296万
-$38,580/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1,734万
-$39,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$2,096万
-$40,707/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr"/>
-      <c r="O6" s="18" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t>G3 | 584呎 (2房)
-$2,296万
-$39,317/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="Q6" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R6" s="18" t="inlineStr">
-        <is>
-          <t>G6 | 1158呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S6" s="16" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>S1 | 1320呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="U6" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 1060呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>7&amp;8/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6,287万
-$39,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7,739万
-$47,132/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7,628万
-$47,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8,325万
-$52,194/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8,330万
-$52,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="16" t="inlineStr"/>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" s="16" t="inlineStr"/>
-      <c r="S7" s="16" t="inlineStr"/>
-      <c r="T7" s="16" t="inlineStr"/>
-      <c r="U7" s="16" t="inlineStr"/>
-      <c r="V7" s="19" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9,144万
-$56,866/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$2,166万
-$38,615/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,547万
-$35,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1,271万
-$37,821/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1,700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1,880万
-$36,515/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr"/>
-      <c r="O8" s="18" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P8" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1,775万
-$35,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="Q8" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R8" s="18" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S8" s="16" t="inlineStr"/>
-      <c r="T8" s="19" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5,241万
-$40,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U8" s="19" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4,169万
-$42,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="V8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$2,124万
-$37,857/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,589万
-$36,522/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,725万
-$36,778/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1,246万
-$37,080/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1,667万
-$38,406/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M9" s="19" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1,844万
-$35,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr"/>
-      <c r="O9" s="18" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P9" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 585呎 (2房)
-$2,028万
-$34,663/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="Q9" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R9" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4,086万
-$36,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S9" s="16" t="inlineStr"/>
-      <c r="T9" s="19" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5,952万
-$46,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U9" s="19" t="inlineStr">
-        <is>
-          <t>S2 | 1061呎 (3房)
-$4,615万
-$43,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="V9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr"/>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1,905万
-$33,961/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,487万
-$34,175/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,547万
-$32,991/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1,222万
-$36,354/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1,634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1,807万
-$35,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4,002万
-$41,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P10" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1,710万
-$34,066/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3,859万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S10" s="16" t="inlineStr"/>
-      <c r="T10" s="19" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5,823万
-$45,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U10" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>5&amp;6/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6,384万
-$40,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4,815万
-$30,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5,358万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4,933万
-$31,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5,211万
-$33,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6,019万
-$38,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
-      <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr"/>
-      <c r="P11" s="16" t="inlineStr"/>
-      <c r="Q11" s="16" t="inlineStr"/>
-      <c r="R11" s="16" t="inlineStr"/>
-      <c r="S11" s="16" t="inlineStr"/>
-      <c r="T11" s="16" t="inlineStr"/>
-      <c r="U11" s="16" t="inlineStr"/>
-      <c r="V11" s="19" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6,678万
-$42,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr"/>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$2,041万
-$36,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,458万
-$33,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,517万
-$32,345/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1,090万
-$32,452/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1,594万
-$36,733/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1,763万
-$34,241/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="inlineStr"/>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$3,904万
-$40,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P12" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 585呎 (2房)
-$1,954万
-$33,397/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R12" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3,836万
-$33,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S12" s="16" t="inlineStr"/>
-      <c r="T12" s="19" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5,047万
-$39,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U12" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 1061呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6,065万
-$38,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4,687万
-$29,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5,834万
-$37,021/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4,743万
-$30,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4,978万
-$31,525/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4,752万
-$30,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
-      <c r="M13" s="16" t="inlineStr"/>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8,387万
-$38,403/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr"/>
-      <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr"/>
-      <c r="R13" s="16" t="inlineStr"/>
-      <c r="S13" s="16" t="inlineStr"/>
-      <c r="T13" s="16" t="inlineStr"/>
-      <c r="U13" s="16" t="inlineStr"/>
-      <c r="V13" s="19" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6,519万
-$41,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr"/>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1,992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1,566万
-$35,991/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1,618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1,104万
-$37,054/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1,633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1,964万
-$41,166/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="inlineStr"/>
-      <c r="O14" s="18" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P14" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1,648万
-$32,825/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="Q14" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4,670万
-$41,143/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S14" s="16" t="inlineStr"/>
-      <c r="T14" s="19" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5,694万
-$44,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="U14" s="18" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>B&amp;G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="16" t="inlineStr"/>
-      <c r="O15" s="16" t="inlineStr"/>
-      <c r="P15" s="16" t="inlineStr"/>
-      <c r="Q15" s="16" t="inlineStr"/>
-      <c r="R15" s="16" t="inlineStr"/>
-      <c r="S15" s="18" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="T15" s="16" t="inlineStr"/>
-      <c r="U15" s="16" t="inlineStr"/>
-      <c r="V15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr"/>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
-      <c r="M16" s="16" t="inlineStr"/>
-      <c r="N16" s="16" t="inlineStr"/>
-      <c r="O16" s="16" t="inlineStr"/>
-      <c r="P16" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1,876万
-$32,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="Q16" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R16" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4,545万
-$39,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S16" s="16" t="inlineStr"/>
-      <c r="T16" s="16" t="inlineStr"/>
-      <c r="U16" s="16" t="inlineStr"/>
-      <c r="V16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5,420万
-$35,992/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5,450万
-$36,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5,253万
-$35,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6,121万
-$41,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5,666万
-$38,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6,134万
-$41,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr"/>
-      <c r="N17" s="16" t="inlineStr"/>
-      <c r="O17" s="16" t="inlineStr"/>
-      <c r="P17" s="16" t="inlineStr"/>
-      <c r="Q17" s="16" t="inlineStr"/>
-      <c r="R17" s="16" t="inlineStr"/>
-      <c r="S17" s="16" t="inlineStr"/>
-      <c r="T17" s="16" t="inlineStr"/>
-      <c r="U17" s="16" t="inlineStr"/>
-      <c r="V17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr"/>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr"/>
-      <c r="O18" s="16" t="inlineStr"/>
-      <c r="P18" s="19" t="inlineStr">
-        <is>
-          <t>G3 | 467呎 (2房)
-$1,795万
-$38,428/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="Q18" s="18" t="inlineStr">
-        <is>
-          <t>G5 | 831呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R18" s="19" t="inlineStr">
-        <is>
-          <t>G6 | 1160呎 (4+房)
-$5,220万
-$45,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="S18" s="16" t="inlineStr"/>
-      <c r="T18" s="16" t="inlineStr"/>
-      <c r="U18" s="16" t="inlineStr"/>
-      <c r="V18" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="滶蕴" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5651,4 +5830,1356 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>滶蕴 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>ROSA VILLA</t>
+        </is>
+      </c>
+      <c r="T4" s="19" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="U4" s="19" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="V4" s="19" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 560呎 (2房)
+$2206万
+$39,388/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1724万
+$39,637/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1795万
+$38,264/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1296万
+$38,580/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1734万
+$39,956/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$2096万
+$40,707/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr"/>
+      <c r="O5" s="22" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t>G3 | 584呎 (2房)
+$2296万
+$39,317/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>G6 | 1158呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S5" s="20" t="inlineStr"/>
+      <c r="T5" s="22" t="inlineStr">
+        <is>
+          <t>S1 | 1320呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="U5" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 1060呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$2166万
+$38,615/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$2124万
+$37,857/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1589万
+$36,522/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1725万
+$36,778/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1246万
+$37,080/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1667万
+$38,406/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1844万
+$35,800/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 585呎 (2房)
+$2028万
+$34,663/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4086万
+$36,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5952万
+$46,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U8" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 1061呎 (3房)
+$4615万
+$43,500/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="V8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$2041万
+$36,387/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1458万
+$33,506/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1517万
+$32,345/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1090万
+$32,452/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1594万
+$36,733/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1763万
+$34,241/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$3904万
+$40,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 585呎 (2房)
+$1954万
+$33,397/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R11" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3836万
+$33,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5047万
+$39,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U11" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 1061呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1566万
+$35,991/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1104万
+$37,054/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1964万
+$41,166/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr"/>
+      <c r="N14" s="20" t="inlineStr"/>
+      <c r="O14" s="20" t="inlineStr"/>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="T14" s="20" t="inlineStr"/>
+      <c r="U14" s="20" t="inlineStr"/>
+      <c r="V14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+      <c r="K15" s="20" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr"/>
+      <c r="M15" s="20" t="inlineStr"/>
+      <c r="N15" s="20" t="inlineStr"/>
+      <c r="O15" s="20" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
+      <c r="T15" s="20" t="inlineStr"/>
+      <c r="U15" s="20" t="inlineStr"/>
+      <c r="V15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
+      <c r="K16" s="20" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr"/>
+      <c r="M16" s="20" t="inlineStr"/>
+      <c r="N16" s="20" t="inlineStr"/>
+      <c r="O16" s="20" t="inlineStr"/>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="20" t="inlineStr"/>
+      <c r="T16" s="20" t="inlineStr"/>
+      <c r="U16" s="20" t="inlineStr"/>
+      <c r="V16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr"/>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
+      <c r="K17" s="20" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr"/>
+      <c r="M17" s="20" t="inlineStr"/>
+      <c r="N17" s="20" t="inlineStr"/>
+      <c r="O17" s="20" t="inlineStr"/>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 467呎 (2房)
+$1795万
+$38,428/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 831呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1160呎 (4+房)
+$5220万
+$45,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S17" s="20" t="inlineStr"/>
+      <c r="T17" s="20" t="inlineStr"/>
+      <c r="U17" s="20" t="inlineStr"/>
+      <c r="V17" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -6163,16 +6163,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $2166万
@@ -6180,7 +6264,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -6188,7 +6272,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -6196,7 +6280,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -6204,7 +6288,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -6212,7 +6296,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -6220,8 +6304,8 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -6229,7 +6313,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -6237,7 +6321,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -6245,7 +6329,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -6253,8 +6337,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -6262,7 +6346,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -6270,91 +6354,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -6430,7 +6430,7 @@
           <t>G3 | 585呎 (2房)
 $2028万
 $34,663/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -6779,16 +6779,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -6796,7 +6880,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1566万
@@ -6804,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -6812,7 +6896,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1104万
@@ -6820,7 +6904,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -6828,7 +6912,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="21" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1964万
@@ -6836,8 +6920,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -6845,7 +6929,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -6853,7 +6937,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -6861,7 +6945,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -6869,8 +6953,8 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -6878,7 +6962,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="U12" s="22" t="inlineStr">
+      <c r="U13" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -6886,96 +6970,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr"/>
@@ -6992,17 +6992,31 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -7010,7 +7024,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -7027,31 +7041,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q15" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -943,7 +1047,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -959,6 +1063,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>20435290</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>34992</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1009,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1055,6 +1195,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18657960</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>36229</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1101,6 +1257,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>15433490</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>35561</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1147,6 +1319,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>11537070</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>34337</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1193,6 +1381,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>15971940</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>34055</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1223,7 +1427,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1239,6 +1443,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>15345380</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>35277</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1285,6 +1505,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>19630730</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>35055</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1331,6 +1567,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>91440000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>56866</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1377,6 +1629,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>41692500</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>42500</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1423,6 +1691,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>52407000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1473,6 +1757,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1523,6 +1827,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1569,6 +1893,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>17749000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>35357</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1619,6 +1959,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1669,6 +2029,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1715,6 +2095,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>18805000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>36515</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1761,6 +2157,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>15130000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>34862</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1807,6 +2219,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>11310120</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>33661</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1853,6 +2281,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>15659550</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>33389</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1899,6 +2343,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>15466000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>35554</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1929,7 +2389,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1945,6 +2405,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>19280070</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>34367</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1995,6 +2471,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2041,6 +2537,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>83300000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>52193</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2087,6 +2599,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>83250000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>52194</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2133,6 +2661,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>76278000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>47883</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2179,6 +2723,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>77390000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>47132</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2225,6 +2785,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>62868000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>39000</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2271,6 +2847,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>46154000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>43500</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2317,6 +2909,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>59524000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>46000</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2352,7 +2960,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2363,6 +2971,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>40860000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2413,6 +3037,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2459,6 +3103,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>20278000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>34663</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2509,6 +3169,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2555,6 +3235,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>18437000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>35800</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2601,6 +3297,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>14834520</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>34181</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2647,6 +3359,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>11088510</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>33002</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2677,7 +3405,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2693,6 +3421,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>15351610</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>32733</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2739,6 +3483,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>15887000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>36522</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2785,6 +3545,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>18901820</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>33693</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2831,6 +3607,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>66780000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2881,6 +3673,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2927,6 +3739,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>58230000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2973,6 +3801,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>38590000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3023,6 +3867,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3069,6 +3933,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>17101000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>34066</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3115,6 +3995,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>40016000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3165,6 +4061,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3211,6 +4127,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>18074000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>35095</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3257,6 +4189,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>14542600</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>33508</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3303,6 +4251,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>10871350</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>32355</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3338,7 +4302,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3349,6 +4313,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>15473000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>32991</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3395,6 +4375,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>14866000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>34175</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3441,6 +4437,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>19052000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>33961</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3487,6 +4499,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>60192000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3533,6 +4561,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>52107000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3579,6 +4623,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>49327200</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>31200</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3625,6 +4685,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>53584000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3671,6 +4747,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>48150000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3717,6 +4809,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>63840000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3767,6 +4875,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3813,6 +4941,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>50466000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>39000</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3859,6 +5003,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>38363000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>33800</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3909,6 +5069,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3955,6 +5135,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>19537000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>33397</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4001,6 +5197,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>39040000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4047,6 +5259,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>17634000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>34241</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4093,6 +5321,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>14188380</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>32692</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4139,6 +5383,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>10904000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>32452</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4185,6 +5445,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>15170000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>32345</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4231,6 +5507,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>14575000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>33506</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4277,6 +5569,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>18167570</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>32384</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4323,6 +5631,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>65190000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4373,6 +5697,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4419,6 +5763,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>56936000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>44000</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4465,6 +5825,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>46697500</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>41143</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4515,6 +5891,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4561,6 +5957,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>16478000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>32825</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4611,6 +6023,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4657,6 +6089,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>83872000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>38403</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4687,7 +6135,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -4703,6 +6151,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>17476040</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>36637</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4749,6 +6213,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>14536370</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>36616</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4795,6 +6275,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>9827380</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>32978</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4841,6 +6337,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>14396640</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>30696</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4887,6 +6399,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>13933840</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>32032</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4933,6 +6461,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>17724350</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>31594</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4979,6 +6523,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>47520000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5025,6 +6585,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>49778000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>31525</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5071,6 +6647,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>47430000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5117,6 +6709,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>58345000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>37021</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5163,6 +6771,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>46866000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>29200</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5209,6 +6833,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>60648000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5259,6 +6899,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5305,6 +6965,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>45452000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>39800</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5355,6 +7031,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5401,6 +7097,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>18765000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>32022</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5447,6 +7159,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>61336000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5493,6 +7221,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>56658000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5539,6 +7283,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>61213000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5585,6 +7345,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>52527000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>35300</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5631,6 +7407,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>54504000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5677,6 +7469,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>54204000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>35992</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5723,6 +7531,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>52200000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5773,6 +7597,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5808,7 +7652,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5819,13 +7663,29 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>17946000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>38428</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5912,12 +7772,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -6068,12 +7928,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1724万
 $39,637/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -6117,12 +7977,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="P5" s="22" t="inlineStr">
         <is>
           <t>G3 | 584呎 (2房)
 $2296万
 $39,317/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q5" s="22" t="inlineStr">
@@ -6171,7 +8031,7 @@
           <t>D1 | 1612呎 (4+房)
 $6287万
 $39,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -6179,7 +8039,7 @@
           <t>D2 | 1642呎 (4+房)
 $7739万
 $47,132/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -6187,7 +8047,7 @@
           <t>D3 | 1593呎 (4+房)
 $7628万
 $47,883/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -6195,7 +8055,7 @@
           <t>D5 | 1595呎 (4+房)
 $8325万
 $52,194/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -6203,7 +8063,7 @@
           <t>D6 | 1596呎 (4+房)
 $8330万
 $52,193/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -6240,7 +8100,7 @@
           <t>S3 | 1608呎 (4+房)
 $9144万
 $56,866/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -6256,12 +8116,12 @@
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $2166万
 $38,615/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -6269,7 +8129,7 @@
           <t>E2 | 435呎 (2房)
 $1547万
 $35,554/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -6301,7 +8161,7 @@
           <t>E7 | 515呎 (2房)
 $1880万
 $36,515/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr"/>
@@ -6318,7 +8178,7 @@
           <t>G3 | 502呎 (2房)
 $1775万
 $35,357/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -6343,7 +8203,7 @@
           <t>S1 | 1294呎 (4+房)
 $5241万
 $40,500/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="U7" s="23" t="inlineStr">
@@ -6351,7 +8211,7 @@
           <t>S2 | 981呎 (3房)
 $4169万
 $42,500/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="V7" s="20" t="inlineStr"/>
@@ -6381,15 +8241,15 @@
           <t>E2 | 435呎 (2房)
 $1589万
 $36,522/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1725万
 $36,778/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -6413,7 +8273,7 @@
           <t>E7 | 515呎 (2房)
 $1844万
 $35,800/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr"/>
@@ -6430,7 +8290,7 @@
           <t>G3 | 585呎 (2房)
 $2028万
 $34,663/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -6446,7 +8306,7 @@
           <t>G6 | 1135呎 (4+房)
 $4086万
 $36,000/呎
-(26年-06月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="S8" s="20" t="inlineStr"/>
@@ -6455,7 +8315,7 @@
           <t>S1 | 1294呎 (4+房)
 $5952万
 $46,000/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="U8" s="23" t="inlineStr">
@@ -6463,7 +8323,7 @@
           <t>S2 | 1061呎 (3房)
 $4615万
 $43,500/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr"/>
@@ -6471,40 +8331,124 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
 $33,961/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
 $34,175/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
 $32,991/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -6512,7 +8456,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -6520,32 +8464,32 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
 $35,095/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
 $41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
 $34,066/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q9" s="22" t="inlineStr">
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -6553,24 +8497,24 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
 $34,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
 $45,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="U9" s="22" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -6578,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -6689,7 +8549,7 @@
           <t>E2 | 435呎 (2房)
 $1458万
 $33,506/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -6697,7 +8557,7 @@
           <t>E3 | 469呎 (2房)
 $1517万
 $32,345/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -6705,7 +8565,7 @@
           <t>E5 | 336呎 (1房)
 $1090万
 $32,452/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -6721,7 +8581,7 @@
           <t>E7 | 515呎 (2房)
 $1763万
 $34,241/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr"/>
@@ -6730,7 +8590,7 @@
           <t>G2 | 976呎 (3房)
 $3904万
 $40,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -6738,7 +8598,7 @@
           <t>G3 | 585呎 (2房)
 $1954万
 $33,397/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -6754,7 +8614,7 @@
           <t>G6 | 1135呎 (4+房)
 $3836万
 $33,800/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr"/>
@@ -6763,7 +8623,7 @@
           <t>S1 | 1294呎 (4+房)
 $5047万
 $39,000/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U11" s="22" t="inlineStr">
@@ -6779,100 +8639,16 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -6880,7 +8656,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1566万
@@ -6888,7 +8664,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -6896,7 +8672,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1104万
@@ -6904,7 +8680,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -6912,16 +8688,16 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M13" s="21" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1964万
 $41,166/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -6929,15 +8705,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P13" s="23" t="inlineStr">
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
 $32,825/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q13" s="22" t="inlineStr">
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -6945,24 +8721,24 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R13" s="23" t="inlineStr">
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
 $41,143/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
 $44,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="U13" s="22" t="inlineStr">
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -6970,12 +8746,96 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V13" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr"/>
@@ -6992,31 +8852,17 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q14" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -7024,7 +8870,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -7041,17 +8887,31 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -7067,7 +8927,7 @@
           <t>D1 | 1506呎 (4+房)
 $5420万
 $35,992/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -7075,7 +8935,7 @@
           <t>D2 | 1514呎 (4+房)
 $5450万
 $36,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -7083,7 +8943,7 @@
           <t>D3 | 1488呎 (4+房)
 $5253万
 $35,300/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -7091,7 +8951,7 @@
           <t>D5 | 1493呎 (4+房)
 $6121万
 $41,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -7099,7 +8959,7 @@
           <t>D6 | 1491呎 (4+房)
 $5666万
 $38,000/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -7107,7 +8967,7 @@
           <t>D7 | 1496呎 (4+房)
 $6134万
 $41,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -7151,7 +9011,7 @@
           <t>G3 | 467呎 (2房)
 $1795万
 $38,428/呎
-(26年-06月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="Q17" s="22" t="inlineStr">
@@ -7167,7 +9027,7 @@
           <t>G6 | 1160呎 (4+房)
 $5220万
 $45,000/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$2166万
+$38,615/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$2166万
-$38,615/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="22" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="22" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8331,10 +8331,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8342,7 +8454,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8350,7 +8462,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8358,7 +8470,7 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8366,7 +8478,7 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8374,7 +8486,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8382,13 +8494,13 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,14 +8508,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8411,118 +8523,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-05日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8639,16 +8639,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8656,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1566万
@@ -8664,7 +8748,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1104万
@@ -8680,7 +8764,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8688,7 +8772,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1964万
@@ -8696,8 +8780,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8713,7 +8797,7 @@
 (26年-07月-05日)</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8721,7 +8805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8729,8 +8813,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8738,7 +8822,7 @@
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="U12" s="22" t="inlineStr">
+      <c r="U13" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8746,104 +8830,62 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
+      <c r="V13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
 $41,000/呎
 (26年-06月-25日)</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8855,14 +8897,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8919,57 +8954,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8981,7 +8974,14 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="20" t="inlineStr"/>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -1063,14 +1063,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>20435290</v>
+        <v>21812950</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>34992</v>
+        <v>37351</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18657960</v>
+        <v>19915800</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>36229</v>
+        <v>38671</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15433490</v>
+        <v>16473950</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>35561</v>
+        <v>37958</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1319,14 +1319,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>11537070</v>
+        <v>12314850</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>34337</v>
+        <v>36651</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>15971940</v>
+        <v>17048700</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>34055</v>
+        <v>36351</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1443,14 +1443,14 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>15345380</v>
+        <v>16379900</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>35277</v>
+        <v>37655</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1505,14 +1505,14 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>19630730</v>
+        <v>20954150</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>35055</v>
+        <v>37418</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -2157,14 +2157,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>15130000</v>
+        <v>16150000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>34862</v>
+        <v>37212</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2219,14 +2219,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>11310120</v>
+        <v>12072600</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>33661</v>
+        <v>35930</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2281,14 +2281,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>15659550</v>
+        <v>16715250</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>33389</v>
+        <v>35640</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>19280070</v>
+        <v>20579850</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>34367</v>
+        <v>36684</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -3297,14 +3297,14 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>14834520</v>
+        <v>15834600</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>34181</v>
+        <v>36485</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3359,14 +3359,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11088510</v>
+        <v>11836050</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>33002</v>
+        <v>35226</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>15351610</v>
+        <v>16386550</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>32733</v>
+        <v>34939</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3545,14 +3545,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>18901820</v>
+        <v>20176100</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>33693</v>
+        <v>35965</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -4189,14 +4189,14 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>14542600</v>
+        <v>15523000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>33508</v>
+        <v>35767</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>10871350</v>
+        <v>11604250</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>32355</v>
+        <v>34536</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>14188380</v>
+        <v>15144900</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>32692</v>
+        <v>34896</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5569,14 +5569,14 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>18167570</v>
+        <v>19392350</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>32384</v>
+        <v>34567</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -6151,14 +6151,14 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>17476040</v>
+        <v>18654200</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>36637</v>
+        <v>39107</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6213,14 +6213,14 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>14536370</v>
+        <v>15516350</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>36616</v>
+        <v>39084</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>9827380</v>
+        <v>10489900</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>32978</v>
+        <v>35201</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6337,14 +6337,14 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>14396640</v>
+        <v>15367200</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>30696</v>
+        <v>32766</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6399,14 +6399,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>13933840</v>
+        <v>14873200</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>32032</v>
+        <v>34191</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6461,14 +6461,14 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>17724350</v>
+        <v>18919250</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>31594</v>
+        <v>33724</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $2166万
@@ -8040,7 +8124,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8331,16 +8331,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8348,7 +8432,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8356,7 +8440,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8364,7 +8448,7 @@
 (26年-07月-12日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8372,7 +8456,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8380,7 +8464,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8388,8 +8472,8 @@
 (26年-07月-05日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8397,7 +8481,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8405,7 +8489,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8413,7 +8497,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8421,8 +8505,8 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8430,7 +8514,7 @@
 (26年-07月-01日)</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8438,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8331,10 +8331,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8342,7 +8454,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8350,7 +8462,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8358,7 +8470,7 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8366,7 +8478,7 @@
 (26年-06月-28日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8374,7 +8486,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8382,13 +8494,13 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,14 +8508,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8411,118 +8523,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-05日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8835,57 +8835,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8894,9 +8852,30 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8905,7 +8884,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8922,31 +8901,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8954,15 +8919,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8974,14 +8981,7 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8031,7 +8031,7 @@
           <t>D1 | 1612呎 (4+房)
 $6287万
 $39,000/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -8039,7 +8039,7 @@
           <t>D2 | 1642呎 (4+房)
 $7739万
 $47,132/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -8047,7 +8047,7 @@
           <t>D3 | 1593呎 (4+房)
 $7628万
 $47,883/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -8055,7 +8055,7 @@
           <t>D5 | 1595呎 (4+房)
 $8325万
 $52,194/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -8063,7 +8063,7 @@
           <t>D6 | 1596呎 (4+房)
 $8330万
 $52,193/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -8100,7 +8100,7 @@
           <t>S3 | 1608呎 (4+房)
 $9144万
 $56,866/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
           <t>E2 | 435呎 (2房)
 $1547万
 $35,554/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -8161,7 +8161,7 @@
           <t>E7 | 515呎 (2房)
 $1880万
 $36,515/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
           <t>G3 | 502呎 (2房)
 $1775万
 $35,357/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -8203,7 +8203,7 @@
           <t>S1 | 1294呎 (4+房)
 $5241万
 $40,500/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="U7" s="23" t="inlineStr">
@@ -8211,7 +8211,7 @@
           <t>S2 | 981呎 (3房)
 $4169万
 $42,500/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="V7" s="20" t="inlineStr"/>
@@ -8241,7 +8241,7 @@
           <t>E2 | 435呎 (2房)
 $1589万
 $36,522/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -8273,7 +8273,7 @@
           <t>E7 | 515呎 (2房)
 $1844万
 $35,800/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr"/>
@@ -8290,7 +8290,7 @@
           <t>G3 | 585呎 (2房)
 $2028万
 $34,663/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>G6 | 1135呎 (4+房)
 $4086万
 $36,000/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="S8" s="20" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>S1 | 1294呎 (4+房)
 $5952万
 $46,000/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="U8" s="23" t="inlineStr">
@@ -8323,7 +8323,7 @@
           <t>S2 | 1061呎 (3房)
 $4615万
 $43,500/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr"/>
@@ -8331,40 +8331,124 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
 $33,961/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
 $34,175/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
 $32,991/呎
-(26年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8372,7 +8456,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8380,32 +8464,32 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
 $35,095/呎
-(26年-07月-05日)</t>
-        </is>
-      </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
 $41,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="P9" s="23" t="inlineStr">
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
 $34,066/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q9" s="22" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8413,24 +8497,24 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
 $34,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
 $45,000/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="U9" s="22" t="inlineStr">
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8438,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8549,7 +8549,7 @@
           <t>E2 | 435呎 (2房)
 $1458万
 $33,506/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -8557,7 +8557,7 @@
           <t>E3 | 469呎 (2房)
 $1517万
 $32,345/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -8565,7 +8565,7 @@
           <t>E5 | 336呎 (1房)
 $1090万
 $32,452/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -8581,7 +8581,7 @@
           <t>E7 | 515呎 (2房)
 $1763万
 $34,241/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr"/>
@@ -8590,7 +8590,7 @@
           <t>G2 | 976呎 (3房)
 $3904万
 $40,000/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>G3 | 585呎 (2房)
 $1954万
 $33,397/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -8614,7 +8614,7 @@
           <t>G6 | 1135呎 (4+房)
 $3836万
 $33,800/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr"/>
@@ -8623,7 +8623,7 @@
           <t>S1 | 1294呎 (4+房)
 $5047万
 $39,000/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="U11" s="22" t="inlineStr">
@@ -8647,7 +8647,7 @@
           <t>D1 | 1596呎 (4+房)
 $6065万
 $38,000/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -8655,7 +8655,7 @@
           <t>D2 | 1605呎 (4+房)
 $4687万
 $29,200/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -8663,7 +8663,7 @@
           <t>D3 | 1576呎 (4+房)
 $5834万
 $37,021/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -8671,7 +8671,7 @@
           <t>D5 | 1581呎 (4+房)
 $4743万
 $30,000/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -8679,7 +8679,7 @@
           <t>D6 | 1579呎 (4+房)
 $4978万
 $31,525/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>D7 | 1584呎 (4+房)
 $4752万
 $30,000/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
@@ -8701,7 +8701,7 @@
           <t>G1 | 2184呎 (4+房)
 $8387万
 $38,403/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr"/>
@@ -8716,7 +8716,7 @@
           <t>S3 | 1590呎 (4+房)
 $6519万
 $41,000/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
           <t>G3 | 502呎 (2房)
 $1648万
 $32,825/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -8810,7 +8810,7 @@
           <t>G6 | 1135呎 (4+房)
 $4670万
 $41,143/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="S13" s="20" t="inlineStr"/>
@@ -8819,7 +8819,7 @@
           <t>S1 | 1294呎 (4+房)
 $5694万
 $44,000/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="U13" s="22" t="inlineStr">
@@ -8835,15 +8835,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8852,30 +8894,9 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q14" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8884,7 +8905,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8901,17 +8922,31 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8919,57 +8954,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8981,7 +8974,14 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="20" t="inlineStr"/>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>
@@ -9011,7 +9011,7 @@
           <t>G3 | 467呎 (2房)
 $1795万
 $38,428/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="Q17" s="22" t="inlineStr">
@@ -9027,7 +9027,7 @@
           <t>G6 | 1160呎 (4+房)
 $5220万
 $45,000/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -8031,7 +8031,7 @@
           <t>D1 | 1612呎 (4+房)
 $6287万
 $39,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -8039,7 +8039,7 @@
           <t>D2 | 1642呎 (4+房)
 $7739万
 $47,132/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -8047,7 +8047,7 @@
           <t>D3 | 1593呎 (4+房)
 $7628万
 $47,883/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -8055,7 +8055,7 @@
           <t>D5 | 1595呎 (4+房)
 $8325万
 $52,194/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -8063,7 +8063,7 @@
           <t>D6 | 1596呎 (4+房)
 $8330万
 $52,193/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -8100,7 +8100,7 @@
           <t>S3 | 1608呎 (4+房)
 $9144万
 $56,866/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
           <t>E2 | 435呎 (2房)
 $1547万
 $35,554/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -8161,7 +8161,7 @@
           <t>E7 | 515呎 (2房)
 $1880万
 $36,515/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
           <t>G3 | 502呎 (2房)
 $1775万
 $35,357/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -8203,7 +8203,7 @@
           <t>S1 | 1294呎 (4+房)
 $5241万
 $40,500/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="U7" s="23" t="inlineStr">
@@ -8211,7 +8211,7 @@
           <t>S2 | 981呎 (3房)
 $4169万
 $42,500/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="V7" s="20" t="inlineStr"/>
@@ -8241,7 +8241,7 @@
           <t>E2 | 435呎 (2房)
 $1589万
 $36,522/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -8273,7 +8273,7 @@
           <t>E7 | 515呎 (2房)
 $1844万
 $35,800/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr"/>
@@ -8290,7 +8290,7 @@
           <t>G3 | 585呎 (2房)
 $2028万
 $34,663/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>G6 | 1135呎 (4+房)
 $4086万
 $36,000/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="S8" s="20" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>S1 | 1294呎 (4+房)
 $5952万
 $46,000/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="U8" s="23" t="inlineStr">
@@ -8323,7 +8323,7 @@
           <t>S2 | 1061呎 (3房)
 $4615万
 $43,500/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr"/>
@@ -8331,64 +8331,176 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-05日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
 $40,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
 $30,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
 $34,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
 $31,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
+(26年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
 $33,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
 $38,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr">
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,133 +8508,21 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
 $42,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q10" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
+(26年-06月-29日)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8549,7 +8549,7 @@
           <t>E2 | 435呎 (2房)
 $1458万
 $33,506/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -8557,7 +8557,7 @@
           <t>E3 | 469呎 (2房)
 $1517万
 $32,345/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -8565,7 +8565,7 @@
           <t>E5 | 336呎 (1房)
 $1090万
 $32,452/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -8581,7 +8581,7 @@
           <t>E7 | 515呎 (2房)
 $1763万
 $34,241/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr"/>
@@ -8590,7 +8590,7 @@
           <t>G2 | 976呎 (3房)
 $3904万
 $40,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>G3 | 585呎 (2房)
 $1954万
 $33,397/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -8614,7 +8614,7 @@
           <t>G6 | 1135呎 (4+房)
 $3836万
 $33,800/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr"/>
@@ -8623,7 +8623,7 @@
           <t>S1 | 1294呎 (4+房)
 $5047万
 $39,000/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U11" s="22" t="inlineStr">
@@ -8647,7 +8647,7 @@
           <t>D1 | 1596呎 (4+房)
 $6065万
 $38,000/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -8655,7 +8655,7 @@
           <t>D2 | 1605呎 (4+房)
 $4687万
 $29,200/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -8663,7 +8663,7 @@
           <t>D3 | 1576呎 (4+房)
 $5834万
 $37,021/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -8671,7 +8671,7 @@
           <t>D5 | 1581呎 (4+房)
 $4743万
 $30,000/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -8679,7 +8679,7 @@
           <t>D6 | 1579呎 (4+房)
 $4978万
 $31,525/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>D7 | 1584呎 (4+房)
 $4752万
 $30,000/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
@@ -8701,7 +8701,7 @@
           <t>G1 | 2184呎 (4+房)
 $8387万
 $38,403/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr"/>
@@ -8716,7 +8716,7 @@
           <t>S3 | 1590呎 (4+房)
 $6519万
 $41,000/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
           <t>G3 | 502呎 (2房)
 $1648万
 $32,825/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -8810,7 +8810,7 @@
           <t>G6 | 1135呎 (4+房)
 $4670万
 $41,143/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="S13" s="20" t="inlineStr"/>
@@ -8819,7 +8819,7 @@
           <t>S1 | 1294呎 (4+房)
 $5694万
 $44,000/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="U13" s="22" t="inlineStr">
@@ -8835,57 +8835,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8894,9 +8852,30 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-28日)</t>
+        </is>
+      </c>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8905,7 +8884,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8922,31 +8901,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="Q15" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8954,15 +8919,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8974,14 +8981,7 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>
@@ -9011,7 +9011,7 @@
           <t>G3 | 467呎 (2房)
 $1795万
 $38,428/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="Q17" s="22" t="inlineStr">
@@ -9027,7 +9027,7 @@
           <t>G6 | 1160呎 (4+房)
 $5220万
 $45,000/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr"/>

--- a/files/九龙-石硖尾-滶蕴.xlsx
+++ b/files/九龙-石硖尾-滶蕴.xlsx
@@ -6383,34 +6383,34 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>15656000</v>
+        <v>14325000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>35991</v>
+        <v>32931</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>14873200</v>
+        <v>14325000</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>34191</v>
+        <v>32931</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8740,12 +8740,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
-$1566万
-$35,991/呎
-(在售)</t>
+$1432万
+$32,931/呎
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -8884,15 +8884,57 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8904,14 +8946,7 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8919,57 +8954,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8981,7 +8974,14 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="20" t="inlineStr"/>
+      <c r="S16" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>
